--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92688</v>
+        <v>92690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92690</v>
+        <v>92691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92691</v>
+        <v>92697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92697</v>
+        <v>92701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92701</v>
+        <v>92703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92703</v>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136772194</v>
       </c>
       <c r="B30" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>136771408</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136771442</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>136771750</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136771796</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136771835</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>136771858</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>136772213</v>
       </c>
       <c r="B37" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136771497</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136772194</v>
       </c>
       <c r="B30" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>136771408</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136771442</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>136771750</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>136771796</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136771835</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>136771858</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>136772213</v>
       </c>
       <c r="B37" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136771497</v>
       </c>
       <c r="B38" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -1274,11 +1274,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -3845,11 +3841,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3960,11 +3952,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4075,11 +4063,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4190,11 +4174,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4305,11 +4285,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4420,11 +4396,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4535,11 +4507,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4650,11 +4618,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4879,11 +4843,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -5105,11 +5065,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92718</v>
+        <v>92721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92721</v>
+        <v>92731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>136772194</v>
       </c>
       <c r="B30" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>136771408</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>136771442</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136771750</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>136771796</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136771835</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136771858</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>136772213</v>
       </c>
       <c r="B37" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>136771497</v>
       </c>
       <c r="B38" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92732</v>
+        <v>92735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136771469</v>
       </c>
       <c r="B3" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136771662</v>
       </c>
       <c r="B4" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136772563</v>
       </c>
       <c r="B5" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136771162</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136771260</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136771446</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136771455</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136771598</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136771648</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136771775</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136772626</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136772677</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136771714</v>
       </c>
       <c r="B15" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136771731</v>
       </c>
       <c r="B16" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136771954</v>
       </c>
       <c r="B17" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136772109</v>
       </c>
       <c r="B18" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136772263</v>
       </c>
       <c r="B19" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136772288</v>
       </c>
       <c r="B20" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>136772296</v>
       </c>
       <c r="B21" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136772320</v>
       </c>
       <c r="B22" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136772363</v>
       </c>
       <c r="B23" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>136772520</v>
       </c>
       <c r="B24" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136772645</v>
       </c>
       <c r="B25" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>136771735</v>
       </c>
       <c r="B26" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136772240</v>
       </c>
       <c r="B27" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>136772372</v>
       </c>
       <c r="B28" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>136772461</v>
       </c>
       <c r="B29" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>136772194</v>
       </c>
       <c r="B30" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>136771408</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>136771442</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136771750</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>136771796</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136771835</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>136771858</v>
       </c>
       <c r="B36" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>136772213</v>
       </c>
       <c r="B37" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>136771497</v>
       </c>
       <c r="B38" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 36890-2026 artfynd.xlsx
+++ b/artfynd/A 36890-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136772125</v>
       </c>
       <c r="B2" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>136771523</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>136772401</v>
       </c>
       <c r="B40" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136772702</v>
       </c>
       <c r="B41" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
